--- a/metrics_utility/test/snapshot_tests/CCSP/data/CCSPv2/snapshot_def_2024-04/report.xlsx
+++ b/metrics_utility/test/snapshot_tests/CCSP/data/CCSPv2/snapshot_def_2024-04/report.xlsx
@@ -535,7 +535,7 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Updated: Feb 04, 2025</t>
+          <t>Updated: Mar 04, 2025</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="G7" s="8" t="n">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F268"/>
+  <dimension ref="A1:F259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6488,242 +6488,44 @@
     <row r="258">
       <c r="A258" s="15" t="inlineStr">
         <is>
-          <t>my_first_test 14</t>
+          <t>my_first_test 694</t>
         </is>
       </c>
       <c r="B258" s="15" t="n">
         <v>1</v>
       </c>
       <c r="C258" s="15" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D258" s="15" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E258" s="16" t="n">
-        <v>45399.01062650024</v>
+        <v>45399.4408509534</v>
       </c>
       <c r="F258" s="16" t="n">
-        <v>45399.38562644433</v>
+        <v>45399.4408509534</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="15" t="inlineStr">
         <is>
-          <t>my_first_test 148</t>
+          <t>my_test</t>
         </is>
       </c>
       <c r="B259" s="15" t="n">
         <v>1</v>
       </c>
       <c r="C259" s="15" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D259" s="15" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E259" s="16" t="n">
-        <v>45399.01062649558</v>
+        <v>45399.43640744589</v>
       </c>
       <c r="F259" s="16" t="n">
-        <v>45399.38562643925</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="15" t="inlineStr">
-        <is>
-          <t>my_first_test 15</t>
-        </is>
-      </c>
-      <c r="B260" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C260" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="D260" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E260" s="16" t="n">
-        <v>45399.01062649627</v>
-      </c>
-      <c r="F260" s="16" t="n">
-        <v>45399.38562644007</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="15" t="inlineStr">
-        <is>
-          <t>my_first_test 16</t>
-        </is>
-      </c>
-      <c r="B261" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C261" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="D261" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E261" s="16" t="n">
-        <v>45399.0106264992</v>
-      </c>
-      <c r="F261" s="16" t="n">
-        <v>45399.38562644357</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="15" t="inlineStr">
-        <is>
-          <t>my_first_test 18</t>
-        </is>
-      </c>
-      <c r="B262" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C262" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="D262" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E262" s="16" t="n">
-        <v>45399.01062649854</v>
-      </c>
-      <c r="F262" s="16" t="n">
-        <v>45399.38562644275</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="15" t="inlineStr">
-        <is>
-          <t>my_first_test 26</t>
-        </is>
-      </c>
-      <c r="B263" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C263" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="D263" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E263" s="16" t="n">
-        <v>45399.01062649232</v>
-      </c>
-      <c r="F263" s="16" t="n">
-        <v>45399.38562643561</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="15" t="inlineStr">
-        <is>
-          <t>my_first_test 338</t>
-        </is>
-      </c>
-      <c r="B264" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C264" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="D264" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E264" s="16" t="n">
-        <v>45399.01062649694</v>
-      </c>
-      <c r="F264" s="16" t="n">
-        <v>45399.38562644089</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="15" t="inlineStr">
-        <is>
-          <t>my_first_test 694</t>
-        </is>
-      </c>
-      <c r="B265" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C265" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D265" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E265" s="16" t="n">
-        <v>45399.4408509534</v>
-      </c>
-      <c r="F265" s="16" t="n">
-        <v>45399.4408509534</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="15" t="inlineStr">
-        <is>
-          <t>my_first_test 7</t>
-        </is>
-      </c>
-      <c r="B266" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C266" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="D266" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E266" s="16" t="n">
-        <v>45399.01062649394</v>
-      </c>
-      <c r="F266" s="16" t="n">
-        <v>45399.3856264374</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="15" t="inlineStr">
-        <is>
-          <t>my_first_test 78</t>
-        </is>
-      </c>
-      <c r="B267" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C267" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="D267" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E267" s="16" t="n">
-        <v>45399.01062649785</v>
-      </c>
-      <c r="F267" s="16" t="n">
-        <v>45399.38562644191</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="15" t="inlineStr">
-        <is>
-          <t>my_test</t>
-        </is>
-      </c>
-      <c r="B268" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C268" s="15" t="n">
-        <v>9</v>
-      </c>
-      <c r="D268" s="15" t="n">
-        <v>11</v>
-      </c>
-      <c r="E268" s="16" t="n">
-        <v>45399.4256597221</v>
-      </c>
-      <c r="F268" s="16" t="n">
         <v>45399.4408509517</v>
       </c>
     </row>
@@ -6789,13 +6591,13 @@
         <v>23</v>
       </c>
       <c r="C2" s="15" t="n">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="D2" s="15" t="n">
-        <v>2377</v>
+        <v>2280</v>
       </c>
       <c r="E2" s="15" t="n">
-        <v>4657</v>
+        <v>4560</v>
       </c>
     </row>
     <row r="3">
